--- a/01-product-factory/02-products/budget-planner-expense-tracker/artifacts/budget-planner-expense-tracker-v1.2.xlsx
+++ b/01-product-factory/02-products/budget-planner-expense-tracker/artifacts/budget-planner-expense-tracker-v1.2.xlsx
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="B40" s="38">
-        <f>B4</f>
+        <f>B5</f>
         <v/>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
         </is>
       </c>
       <c r="B41" s="38">
-        <f>B5</f>
+        <f>B7</f>
         <v/>
       </c>
     </row>
